--- a/data/gravel/Reeb Sam's Pants 2025.xlsx
+++ b/data/gravel/Reeb Sam's Pants 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10905"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A732C3EE-CD23-6449-9FEC-1E127E7FFB91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FED7BA7B-BB41-4D45-9927-1A990A249413}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3880" yWindow="500" windowWidth="24920" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="109">
   <si>
     <t>brand</t>
   </si>
@@ -357,6 +357,9 @@
   </si>
   <si>
     <t>a8:g32</t>
+  </si>
+  <si>
+    <t>https://reebcycles.com/cdn/shop/files/25_1_REEB_GravelBike_Snow-2.jpg?v=1747419594&amp;width=1920</t>
   </si>
 </sst>
 </file>
@@ -759,6 +762,11 @@
         <v>76</v>
       </c>
     </row>
+    <row r="6" spans="1:7">
+      <c r="B6" t="s">
+        <v>108</v>
+      </c>
+    </row>
     <row r="7" spans="1:7">
       <c r="A7" t="s">
         <v>5</v>

--- a/data/gravel/Reeb Sam's Pants 2025.xlsx
+++ b/data/gravel/Reeb Sam's Pants 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FED7BA7B-BB41-4D45-9927-1A990A249413}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD759FA8-F5C7-844D-9E9D-3D0E63011803}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3880" yWindow="500" windowWidth="24920" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="111">
   <si>
     <t>brand</t>
   </si>
@@ -360,6 +360,12 @@
   </si>
   <si>
     <t>https://reebcycles.com/cdn/shop/files/25_1_REEB_GravelBike_Snow-2.jpg?v=1747419594&amp;width=1920</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>Lyons, Colorado, USA</t>
   </si>
 </sst>
 </file>
@@ -716,7 +722,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H72"/>
+  <dimension ref="A1:H73"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1567,6 +1573,14 @@
         <v>75</v>
       </c>
     </row>
+    <row r="73" spans="1:2">
+      <c r="A73" t="s">
+        <v>109</v>
+      </c>
+      <c r="B73" t="s">
+        <v>110</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
